--- a/data/dividends_info_20260413.xlsx
+++ b/data/dividends_info_20260413.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>33.56000137329102</v>
+        <v>33.84000015258789</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2681763895028538</v>
+        <v>0.2659574456092823</v>
       </c>
       <c r="J2" t="n">
         <v>336</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>52.84999847412109</v>
+        <v>53.70000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.324503349499181</v>
+        <v>1.303538156526617</v>
       </c>
       <c r="J3" t="n">
         <v>315</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J4" t="n">
         <v>245</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J5" t="n">
         <v>245</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>33.55500030517578</v>
+        <v>33.84000015258789</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2682163587586608</v>
+        <v>0.2659574456092823</v>
       </c>
       <c r="J6" t="n">
         <v>245</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.900000095367432</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I8" t="n">
-        <v>3.389830453681454</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J8" t="n">
         <v>217</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.550000190734863</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I9" t="n">
-        <v>1.081081043927956</v>
+        <v>1.025641042361154</v>
       </c>
       <c r="J9" t="n">
         <v>189</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J10" t="n">
         <v>189</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>33.55500030517578</v>
+        <v>33.84000015258789</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2682163587586608</v>
+        <v>0.2659574456092823</v>
       </c>
       <c r="J11" t="n">
         <v>161</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J12" t="n">
         <v>133</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.570000171661377</v>
+        <v>6.360000133514404</v>
       </c>
       <c r="I13" t="n">
-        <v>3.805174938629898</v>
+        <v>3.930817527543905</v>
       </c>
       <c r="J13" t="n">
         <v>105</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.850000381469727</v>
+        <v>9.822999954223633</v>
       </c>
       <c r="I14" t="n">
-        <v>2.63959380640354</v>
+        <v>2.646849243730342</v>
       </c>
       <c r="J14" t="n">
         <v>98</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.39999961853027</v>
+        <v>16.13999938964844</v>
       </c>
       <c r="I15" t="n">
-        <v>3.658536670464694</v>
+        <v>3.717472259539343</v>
       </c>
       <c r="J15" t="n">
         <v>98</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J16" t="n">
         <v>98</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.28000020980835</v>
+        <v>5.210000038146973</v>
       </c>
       <c r="I18" t="n">
-        <v>2.272727182417209</v>
+        <v>2.303262938989922</v>
       </c>
       <c r="J18" t="n">
         <v>91</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.480000019073486</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="I21" t="n">
-        <v>1.562499993347696</v>
+        <v>1.518438133897318</v>
       </c>
       <c r="J21" t="n">
         <v>84</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>32.15000152587891</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="I22" t="n">
-        <v>0.466562963859453</v>
+        <v>0.4594180489734668</v>
       </c>
       <c r="J22" t="n">
         <v>84</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.050000190734863</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6611570039494726</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J23" t="n">
         <v>77</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>23.47999954223633</v>
+        <v>23.28000068664551</v>
       </c>
       <c r="I24" t="n">
-        <v>4.045996671725311</v>
+        <v>4.080755893383475</v>
       </c>
       <c r="J24" t="n">
         <v>70</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>25.10000038146973</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7768924184716758</v>
+        <v>0.7558139758387714</v>
       </c>
       <c r="J25" t="n">
         <v>70</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.28000020980835</v>
+        <v>5.295000076293945</v>
       </c>
       <c r="I27" t="n">
-        <v>5.49242402417492</v>
+        <v>5.476864888035575</v>
       </c>
       <c r="J27" t="n">
         <v>70</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.171999931335449</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="I28" t="n">
-        <v>3.835091146532793</v>
+        <v>3.818615699641303</v>
       </c>
       <c r="J28" t="n">
         <v>70</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.619999885559082</v>
+        <v>2.611999988555908</v>
       </c>
       <c r="I29" t="n">
-        <v>5.29007656694703</v>
+        <v>5.306278736878078</v>
       </c>
       <c r="J29" t="n">
         <v>70</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>57.15000152587891</v>
+        <v>57.79999923706055</v>
       </c>
       <c r="I30" t="n">
-        <v>1.102362175291843</v>
+        <v>1.089965412311031</v>
       </c>
       <c r="J30" t="n">
         <v>70</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>17.5</v>
+        <v>17.95000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>4.457142857142857</v>
+        <v>4.345403715026188</v>
       </c>
       <c r="J31" t="n">
         <v>70</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>21.69000053405762</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="I32" t="n">
-        <v>3.918856519460803</v>
+        <v>3.840940046246957</v>
       </c>
       <c r="J32" t="n">
         <v>70</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>33.55500030517578</v>
+        <v>33.84000015258789</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2682163587586608</v>
+        <v>0.2659574456092823</v>
       </c>
       <c r="J33" t="n">
         <v>70</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6.760000228881836</v>
+        <v>6.734000205993652</v>
       </c>
       <c r="I34" t="n">
-        <v>2.681952571915646</v>
+        <v>2.692307609949765</v>
       </c>
       <c r="J34" t="n">
         <v>70</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.119999885559082</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I35" t="n">
-        <v>3.201970488477394</v>
+        <v>3.170731781069402</v>
       </c>
       <c r="J35" t="n">
         <v>70</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10.27499961853027</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="I36" t="n">
-        <v>2.695863847045299</v>
+        <v>2.697176121259081</v>
       </c>
       <c r="J36" t="n">
         <v>70</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.047999858856201</v>
+        <v>4.10200023651123</v>
       </c>
       <c r="I37" t="n">
-        <v>2.717391399096577</v>
+        <v>2.681618567958823</v>
       </c>
       <c r="J37" t="n">
         <v>63</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>27.89999961853027</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="I39" t="n">
-        <v>3.978494678052877</v>
+        <v>3.99280586497371</v>
       </c>
       <c r="J39" t="n">
         <v>52</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8669999837875366</v>
+        <v>0.8880000114440918</v>
       </c>
       <c r="I40" t="n">
-        <v>3.460207677160888</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J40" t="n">
         <v>49</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.5260000228881836</v>
+        <v>0.5329999923706055</v>
       </c>
       <c r="I41" t="n">
-        <v>4.372623383875653</v>
+        <v>4.315197059891821</v>
       </c>
       <c r="J41" t="n">
         <v>49</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19</v>
+        <v>19.04999923706055</v>
       </c>
       <c r="I42" t="n">
-        <v>3.157894736842105</v>
+        <v>3.149606425352178</v>
       </c>
       <c r="J42" t="n">
         <v>49</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.654999971389771</v>
+        <v>2.674999952316284</v>
       </c>
       <c r="I43" t="n">
-        <v>6.779661090006652</v>
+        <v>6.728972082565381</v>
       </c>
       <c r="J43" t="n">
         <v>42</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8.399999618530273</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I44" t="n">
-        <v>3.571428733618088</v>
+        <v>3.488371938289734</v>
       </c>
       <c r="J44" t="n">
         <v>42</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>12.80000019073486</v>
+        <v>12.88000011444092</v>
       </c>
       <c r="I45" t="n">
-        <v>1.95312497089617</v>
+        <v>1.940993771573827</v>
       </c>
       <c r="J45" t="n">
         <v>42</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.720000028610229</v>
+        <v>3.789999961853027</v>
       </c>
       <c r="I47" t="n">
-        <v>4.032258033504347</v>
+        <v>3.957783680996692</v>
       </c>
       <c r="J47" t="n">
         <v>42</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>13.75</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="I48" t="n">
-        <v>4.218181818181818</v>
+        <v>4.264705762731166</v>
       </c>
       <c r="J48" t="n">
         <v>42</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.529999971389771</v>
+        <v>2.505000114440918</v>
       </c>
       <c r="I49" t="n">
-        <v>4.11067198324398</v>
+        <v>4.151696417116188</v>
       </c>
       <c r="J49" t="n">
         <v>35</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9.092000007629395</v>
+        <v>8.930000305175781</v>
       </c>
       <c r="I50" t="n">
-        <v>3.189617243253976</v>
+        <v>3.247480292155394</v>
       </c>
       <c r="J50" t="n">
         <v>35</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>35.70999908447266</v>
+        <v>36.11000061035156</v>
       </c>
       <c r="I52" t="n">
-        <v>4.592551223875839</v>
+        <v>4.541678128717243</v>
       </c>
       <c r="J52" t="n">
         <v>35</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>34.47999954223633</v>
+        <v>35.08000183105469</v>
       </c>
       <c r="I53" t="n">
-        <v>5.800464114131141</v>
+        <v>5.701253978354965</v>
       </c>
       <c r="J53" t="n">
         <v>35</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3.98799991607666</v>
+        <v>3.921999931335449</v>
       </c>
       <c r="I54" t="n">
-        <v>2.507522620471332</v>
+        <v>2.54971957549091</v>
       </c>
       <c r="J54" t="n">
         <v>35</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>34.20000076293945</v>
+        <v>34.84999847412109</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4340935575676287</v>
+        <v>0.4259971492114796</v>
       </c>
       <c r="J55" t="n">
         <v>35</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>22.23999977111816</v>
+        <v>22.26000022888184</v>
       </c>
       <c r="I56" t="n">
-        <v>4.136690690054558</v>
+        <v>4.132973901798623</v>
       </c>
       <c r="J56" t="n">
         <v>35</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8.329999923706055</v>
+        <v>8.270000457763672</v>
       </c>
       <c r="I57" t="n">
-        <v>3.60144060921586</v>
+        <v>3.62756932762159</v>
       </c>
       <c r="J57" t="n">
         <v>35</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>80.86000061035156</v>
+        <v>82.13999938964844</v>
       </c>
       <c r="I58" t="n">
-        <v>1.286173623732153</v>
+        <v>1.266131005268871</v>
       </c>
       <c r="J58" t="n">
         <v>35</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>47.86000061035156</v>
+        <v>47.93000030517578</v>
       </c>
       <c r="I59" t="n">
-        <v>1.462599229153787</v>
+        <v>1.460463166165283</v>
       </c>
       <c r="J59" t="n">
         <v>35</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>52.84999847412109</v>
+        <v>53.70000076293945</v>
       </c>
       <c r="I60" t="n">
-        <v>4.162724812711712</v>
+        <v>4.096834206226509</v>
       </c>
       <c r="J60" t="n">
         <v>35</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>8.027000427246094</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I61" t="n">
-        <v>10.71384021708654</v>
+        <v>10.669974630608</v>
       </c>
       <c r="J61" t="n">
         <v>35</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>12.10999965667725</v>
+        <v>12.22799968719482</v>
       </c>
       <c r="I62" t="n">
-        <v>4.624277587747294</v>
+        <v>4.57965337197737</v>
       </c>
       <c r="J62" t="n">
         <v>35</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>9.060000419616699</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I64" t="n">
-        <v>3.311258124783752</v>
+        <v>3.260869632821905</v>
       </c>
       <c r="J64" t="n">
         <v>35</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.319999933242798</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I65" t="n">
-        <v>4.655172547744092</v>
+        <v>4.778761082112308</v>
       </c>
       <c r="J65" t="n">
         <v>35</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>73.5</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="I66" t="n">
-        <v>2.802721088435374</v>
+        <v>2.787550686691951</v>
       </c>
       <c r="J66" t="n">
         <v>35</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>15.27999973297119</v>
+        <v>15.39000034332275</v>
       </c>
       <c r="I67" t="n">
-        <v>4.908377049128147</v>
+        <v>4.873294238264276</v>
       </c>
       <c r="J67" t="n">
         <v>35</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>45.79999923706055</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="I69" t="n">
-        <v>1.855895227422177</v>
+        <v>1.820128449921889</v>
       </c>
       <c r="J69" t="n">
         <v>35</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>34.56000137329102</v>
+        <v>34.27999877929688</v>
       </c>
       <c r="I70" t="n">
-        <v>2.459490643009363</v>
+        <v>2.47958001828562</v>
       </c>
       <c r="J70" t="n">
         <v>35</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>60.15999984741211</v>
+        <v>61.2599983215332</v>
       </c>
       <c r="I71" t="n">
-        <v>2.160904260799997</v>
+        <v>2.122102572018914</v>
       </c>
       <c r="J71" t="n">
         <v>35</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>7.619999885559082</v>
+        <v>7.519999980926514</v>
       </c>
       <c r="I72" t="n">
-        <v>7.874015866287349</v>
+        <v>7.978723424492297</v>
       </c>
       <c r="J72" t="n">
         <v>35</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>5.849999904632568</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I73" t="n">
-        <v>8.034188165162375</v>
+        <v>7.704918153245615</v>
       </c>
       <c r="J73" t="n">
         <v>35</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>5.900000095367432</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I74" t="n">
-        <v>3.389830453681454</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J74" t="n">
         <v>35</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>22.3799991607666</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="I75" t="n">
-        <v>4.468275413312152</v>
+        <v>4.537204893197135</v>
       </c>
       <c r="J75" t="n">
         <v>35</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>4.46999979019165</v>
+        <v>4.570000171661377</v>
       </c>
       <c r="I76" t="n">
-        <v>4.809843626207014</v>
+        <v>4.704595009278499</v>
       </c>
       <c r="J76" t="n">
         <v>35</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>24.19499969482422</v>
+        <v>24.01000022888184</v>
       </c>
       <c r="I77" t="n">
-        <v>1.115933058092819</v>
+        <v>1.124531434511253</v>
       </c>
       <c r="J77" t="n">
         <v>35</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>7.639999866485596</v>
+        <v>7.800000190734863</v>
       </c>
       <c r="I78" t="n">
-        <v>2.617801092868345</v>
+        <v>2.564102501402085</v>
       </c>
       <c r="J78" t="n">
         <v>35</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>9.614999771118164</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I79" t="n">
-        <v>2.496099903412577</v>
+        <v>2.474226852775394</v>
       </c>
       <c r="J79" t="n">
         <v>35</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>20.51000022888184</v>
+        <v>20.95000076293945</v>
       </c>
       <c r="I80" t="n">
-        <v>3.851779576713682</v>
+        <v>3.770882917567764</v>
       </c>
       <c r="J80" t="n">
         <v>35</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>4.699999809265137</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="I81" t="n">
-        <v>1.97872348455565</v>
+        <v>1.99143465697336</v>
       </c>
       <c r="J81" t="n">
         <v>35</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5.550000190734863</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I82" t="n">
-        <v>1.081081043927956</v>
+        <v>1.025641042361154</v>
       </c>
       <c r="J82" t="n">
         <v>35</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>37.27999877929688</v>
+        <v>37.38000106811523</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9388412324583268</v>
+        <v>0.9363295612598216</v>
       </c>
       <c r="J83" t="n">
         <v>35</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>7.360000133514404</v>
+        <v>7.355000019073486</v>
       </c>
       <c r="I84" t="n">
-        <v>7.53124986337903</v>
+        <v>7.536369796907567</v>
       </c>
       <c r="J84" t="n">
         <v>35</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>2.069999933242798</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I85" t="n">
-        <v>2.898550818115528</v>
+        <v>2.912621440126959</v>
       </c>
       <c r="J85" t="n">
         <v>35</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>12.14999961853027</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I86" t="n">
-        <v>1.646090586661212</v>
+        <v>1.562499976716936</v>
       </c>
       <c r="J86" t="n">
         <v>35</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.860000133514404</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I87" t="n">
-        <v>1.757679140840361</v>
+        <v>1.769759397972623</v>
       </c>
       <c r="J87" t="n">
         <v>35</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5.579999923706055</v>
+        <v>5.656000137329102</v>
       </c>
       <c r="I88" t="n">
-        <v>3.405017967702913</v>
+        <v>3.359264416314575</v>
       </c>
       <c r="J88" t="n">
         <v>35</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>10.4399995803833</v>
+        <v>10.50500011444092</v>
       </c>
       <c r="I89" t="n">
-        <v>4.137931200799332</v>
+        <v>4.112327418313325</v>
       </c>
       <c r="J89" t="n">
         <v>35</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>26.14999961853027</v>
+        <v>26.55999946594238</v>
       </c>
       <c r="I90" t="n">
-        <v>1.682600406954536</v>
+        <v>1.656626539334865</v>
       </c>
       <c r="J90" t="n">
         <v>35</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>8.140000343322754</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="I92" t="n">
-        <v>5.773955530426251</v>
+        <v>5.608591808848162</v>
       </c>
       <c r="J92" t="n">
         <v>35</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>53.08000183105469</v>
+        <v>53.04000091552734</v>
       </c>
       <c r="I93" t="n">
-        <v>2.637528168246829</v>
+        <v>2.639517299838796</v>
       </c>
       <c r="J93" t="n">
         <v>35</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3.371000051498413</v>
+        <v>3.456000089645386</v>
       </c>
       <c r="I94" t="n">
-        <v>8.899436233074209</v>
+        <v>8.680555330390122</v>
       </c>
       <c r="J94" t="n">
         <v>35</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>12.89999961853027</v>
+        <v>12.94999980926514</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9302325856477186</v>
+        <v>0.9266409402890141</v>
       </c>
       <c r="J95" t="n">
         <v>35</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3.490000009536743</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I96" t="n">
-        <v>4.871060158609155</v>
+        <v>4.941860382914093</v>
       </c>
       <c r="J96" t="n">
         <v>35</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>20</v>
+        <v>19.42000007629395</v>
       </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>3.60453139675572</v>
       </c>
       <c r="J97" t="n">
         <v>35</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2.640000104904175</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I98" t="n">
-        <v>1.325757523076705</v>
+        <v>1.305970116722794</v>
       </c>
       <c r="J98" t="n">
         <v>35</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6.130000114440918</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I99" t="n">
-        <v>5.383360421520929</v>
+        <v>5.409836150151177</v>
       </c>
       <c r="J99" t="n">
         <v>35</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.9679999947547913</v>
+        <v>0.9639999866485596</v>
       </c>
       <c r="I100" t="n">
-        <v>7.231404997861807</v>
+        <v>7.261410888952589</v>
       </c>
       <c r="J100" t="n">
         <v>35</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>48.36000061035156</v>
+        <v>48.65999984741211</v>
       </c>
       <c r="I101" t="n">
-        <v>1.468155481883974</v>
+        <v>1.459103991422968</v>
       </c>
       <c r="J101" t="n">
         <v>35</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>82.40000152587891</v>
+        <v>84.40000152587891</v>
       </c>
       <c r="I102" t="n">
-        <v>1.638349484224237</v>
+        <v>1.599526037432665</v>
       </c>
       <c r="J102" t="n">
         <v>35</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I103" t="n">
-        <v>1.142857142857143</v>
+        <v>1.126760578514967</v>
       </c>
       <c r="J103" t="n">
         <v>35</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>4.193999767303467</v>
+        <v>4.15500020980835</v>
       </c>
       <c r="I105" t="n">
-        <v>4.053409857704917</v>
+        <v>4.09145587041598</v>
       </c>
       <c r="J105" t="n">
         <v>35</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>58.70000076293945</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7666098707857425</v>
+        <v>0.771869649895194</v>
       </c>
       <c r="J107" t="n">
         <v>35</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>4.599999904632568</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8695652354191747</v>
+        <v>0.8849557559467237</v>
       </c>
       <c r="J108" t="n">
         <v>35</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>32.11999893188477</v>
+        <v>32.38000106811523</v>
       </c>
       <c r="I109" t="n">
-        <v>3.268991391396622</v>
+        <v>3.24274232663303</v>
       </c>
       <c r="J109" t="n">
         <v>35</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>19.1200008392334</v>
+        <v>19.25</v>
       </c>
       <c r="I111" t="n">
-        <v>1.987447611509811</v>
+        <v>1.974025974025974</v>
       </c>
       <c r="J111" t="n">
         <v>35</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>25.76000022888184</v>
+        <v>25.72999954223633</v>
       </c>
       <c r="I112" t="n">
-        <v>2.329192525888592</v>
+        <v>2.331908319761482</v>
       </c>
       <c r="J112" t="n">
         <v>35</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>30</v>
+        <v>30.60000038146973</v>
       </c>
       <c r="I113" t="n">
-        <v>1.166666666666667</v>
+        <v>1.143790835414327</v>
       </c>
       <c r="J113" t="n">
         <v>35</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.920000076293945</v>
+        <v>3</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5821917656103744</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J114" t="n">
         <v>35</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>2.789999961853027</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3584229439687277</v>
+        <v>0.3676470549564461</v>
       </c>
       <c r="J115" t="n">
         <v>35</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>21.32999992370605</v>
+        <v>21.6299991607666</v>
       </c>
       <c r="I116" t="n">
-        <v>5.250820459475191</v>
+        <v>5.177993728411709</v>
       </c>
       <c r="J116" t="n">
         <v>35</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>2.507999897003174</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="I118" t="n">
-        <v>10.36682658203758</v>
+        <v>10.31746039555156</v>
       </c>
       <c r="J118" t="n">
         <v>35</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>2.046000003814697</v>
+        <v>2.072000026702881</v>
       </c>
       <c r="I119" t="n">
-        <v>4.511241438314261</v>
+        <v>4.454633147224161</v>
       </c>
       <c r="J119" t="n">
         <v>35</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>9.199999809265137</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I120" t="n">
-        <v>3.804347904958889</v>
+        <v>3.880265878465104</v>
       </c>
       <c r="J120" t="n">
         <v>28</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.980000019073486</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I121" t="n">
-        <v>1.927710835990328</v>
+        <v>1.935483856082087</v>
       </c>
       <c r="J121" t="n">
         <v>28</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>5.900000095367432</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I122" t="n">
-        <v>5.08474568052218</v>
+        <v>4.958677529621045</v>
       </c>
       <c r="J122" t="n">
         <v>28</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>9</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J124" t="n">
         <v>28</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>16.1200008392334</v>
+        <v>16.18000030517578</v>
       </c>
       <c r="I126" t="n">
-        <v>3.101736811223256</v>
+        <v>3.090234799563361</v>
       </c>
       <c r="J126" t="n">
         <v>28</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.680000066757202</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I128" t="n">
-        <v>4.10447750970021</v>
+        <v>4.044117604520907</v>
       </c>
       <c r="J128" t="n">
         <v>28</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>4.5</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="I130" t="n">
-        <v>2.111111111111111</v>
+        <v>2.087912000387338</v>
       </c>
       <c r="J130" t="n">
         <v>28</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1.139999985694885</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="I131" t="n">
-        <v>2.631578980390385</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J131" t="n">
         <v>28</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>7.449999809265137</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I132" t="n">
-        <v>1.208053722203753</v>
+        <v>1.192052950017741</v>
       </c>
       <c r="J132" t="n">
         <v>28</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>7.849999904632568</v>
+        <v>7.75</v>
       </c>
       <c r="I133" t="n">
-        <v>1.273885365794545</v>
+        <v>1.290322580645161</v>
       </c>
       <c r="J133" t="n">
         <v>28</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>7.139999866485596</v>
+        <v>7.090000152587891</v>
       </c>
       <c r="I134" t="n">
-        <v>3.081232550614696</v>
+        <v>3.102961851414047</v>
       </c>
       <c r="J134" t="n">
         <v>28</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>3.565000057220459</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I135" t="n">
-        <v>4.488078469338034</v>
+        <v>4.597701124225808</v>
       </c>
       <c r="J135" t="n">
         <v>21</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>24.70000076293945</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="I136" t="n">
-        <v>2.469635551247676</v>
+        <v>2.459677495023589</v>
       </c>
       <c r="J136" t="n">
         <v>21</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>3.019999980926514</v>
+        <v>3.140000104904175</v>
       </c>
       <c r="I137" t="n">
-        <v>4.966887448588033</v>
+        <v>4.777069904097268</v>
       </c>
       <c r="J137" t="n">
         <v>21</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>12.25</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="I138" t="n">
-        <v>5.714285714285714</v>
+        <v>5.857740679269905</v>
       </c>
       <c r="J138" t="n">
         <v>21</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.140000343322754</v>
+        <v>9.149999618530273</v>
       </c>
       <c r="I139" t="n">
-        <v>5.585338958689939</v>
+        <v>5.579235205279708</v>
       </c>
       <c r="J139" t="n">
         <v>21</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>7.75</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="I140" t="n">
-        <v>3.483870967741936</v>
+        <v>3.400503753831438</v>
       </c>
       <c r="J140" t="n">
         <v>21</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>5.389999866485596</v>
+        <v>5.554999828338623</v>
       </c>
       <c r="I141" t="n">
-        <v>6.493506654355598</v>
+        <v>6.300630257709246</v>
       </c>
       <c r="J141" t="n">
         <v>21</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>18.79999923706055</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I143" t="n">
-        <v>3.989361864023487</v>
+        <v>4.032257981818046</v>
       </c>
       <c r="J143" t="n">
         <v>21</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>11.97999954223633</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="I146" t="n">
-        <v>1.645818092937874</v>
+        <v>1.629495816396419</v>
       </c>
       <c r="J146" t="n">
         <v>21</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>28.35000038146973</v>
+        <v>28.70000076293945</v>
       </c>
       <c r="I147" t="n">
-        <v>3.880070494528063</v>
+        <v>3.832752511353377</v>
       </c>
       <c r="J147" t="n">
         <v>21</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>19.65999984741211</v>
+        <v>19.55999946594238</v>
       </c>
       <c r="I148" t="n">
-        <v>2.543235014652435</v>
+        <v>2.556237288608282</v>
       </c>
       <c r="J148" t="n">
         <v>21</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>44.34999847412109</v>
+        <v>46.04999923706055</v>
       </c>
       <c r="I149" t="n">
-        <v>1.059752009403681</v>
+        <v>1.020629767180862</v>
       </c>
       <c r="J149" t="n">
         <v>21</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>79.80000305175781</v>
+        <v>80.19999694824219</v>
       </c>
       <c r="I150" t="n">
-        <v>1.503759340988605</v>
+        <v>1.496259408556376</v>
       </c>
       <c r="J150" t="n">
         <v>21</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>23.25</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="I151" t="n">
-        <v>1.161290322580645</v>
+        <v>1.179039320950559</v>
       </c>
       <c r="J151" t="n">
         <v>21</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>10.55000019073486</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I152" t="n">
-        <v>3.601895669478002</v>
+        <v>3.671497449220761</v>
       </c>
       <c r="J152" t="n">
         <v>21</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>27.14999961853027</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I153" t="n">
-        <v>1.104972391215967</v>
+        <v>1.094890526192248</v>
       </c>
       <c r="J153" t="n">
         <v>21</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>0.1524000018835068</v>
+        <v>0.1516000032424927</v>
       </c>
       <c r="I154" t="n">
-        <v>4.593175796251458</v>
+        <v>4.617414149261665</v>
       </c>
       <c r="J154" t="n">
         <v>14</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>7.480000019073486</v>
+        <v>7.389999866485596</v>
       </c>
       <c r="I155" t="n">
-        <v>2.139037427700682</v>
+        <v>2.165087995814673</v>
       </c>
       <c r="J155" t="n">
         <v>14</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>2.180000066757202</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I156" t="n">
-        <v>2.981651284840964</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J156" t="n">
         <v>14</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>7.880000114440918</v>
+        <v>7.78000020980835</v>
       </c>
       <c r="I157" t="n">
-        <v>3.172588786411933</v>
+        <v>3.213367522597515</v>
       </c>
       <c r="J157" t="n">
         <v>14</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1.389999985694885</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I158" t="n">
-        <v>5.035971274849027</v>
+        <v>4.827586048139834</v>
       </c>
       <c r="J158" t="n">
         <v>14</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>6.730000019073486</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="I159" t="n">
-        <v>7.429420484144882</v>
+        <v>7.385524393038065</v>
       </c>
       <c r="J159" t="n">
         <v>7</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>18.36000061035156</v>
+        <v>18.77000045776367</v>
       </c>
       <c r="I160" t="n">
-        <v>3.540304893200947</v>
+        <v>3.462972744527272</v>
       </c>
       <c r="J160" t="n">
         <v>7</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>12.51500034332275</v>
+        <v>12.53999996185303</v>
       </c>
       <c r="I161" t="n">
-        <v>4.3148220949759</v>
+        <v>4.306220108793402</v>
       </c>
       <c r="J161" t="n">
         <v>7</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>6.585999965667725</v>
+        <v>6.613999843597412</v>
       </c>
       <c r="I162" t="n">
-        <v>1.518372312804309</v>
+        <v>1.511944396200789</v>
       </c>
       <c r="J162" t="n">
         <v>7</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>8.420000076293945</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="I163" t="n">
-        <v>1.900237512473086</v>
+        <v>1.86480188138381</v>
       </c>
       <c r="J163" t="n">
         <v>7</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>295.8500061035156</v>
+        <v>299.1499938964844</v>
       </c>
       <c r="I164" t="n">
-        <v>1.221902966172372</v>
+        <v>1.208423892280241</v>
       </c>
       <c r="J164" t="n">
         <v>7</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>14.57999992370605</v>
+        <v>14.89000034332275</v>
       </c>
       <c r="I166" t="n">
-        <v>4.012345700008072</v>
+        <v>3.928811192152432</v>
       </c>
       <c r="J166" t="n">
         <v>7</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>17.8700008392334</v>
+        <v>17.97999954223633</v>
       </c>
       <c r="I167" t="n">
-        <v>3.525461502032175</v>
+        <v>3.503893303890716</v>
       </c>
       <c r="J167" t="n">
         <v>7</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>119</v>
+        <v>119.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7563025210084033</v>
+        <v>0.7518797184173334</v>
       </c>
       <c r="J168" t="n">
         <v>7</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>67.19999694824219</v>
+        <v>68.18000030517578</v>
       </c>
       <c r="I169" t="n">
-        <v>2.560714402004169</v>
+        <v>2.523907292897692</v>
       </c>
       <c r="J169" t="n">
         <v>7</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>26.60000038146973</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I170" t="n">
-        <v>0.526315781925807</v>
+        <v>0.5303030379657029</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1.889999985694885</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="I172" t="n">
-        <v>1.798941812557709</v>
+        <v>1.780104743150475</v>
       </c>
       <c r="J172" t="n">
         <v>-14</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>24.20499992370605</v>
+        <v>24.01000022888184</v>
       </c>
       <c r="I173" t="n">
-        <v>1.074158235156033</v>
+        <v>1.082882122121947</v>
       </c>
       <c r="J173" t="n">
         <v>-21</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>33.55500030517578</v>
+        <v>33.84000015258789</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2682163587586608</v>
+        <v>0.2659574456092823</v>
       </c>
       <c r="J174" t="n">
         <v>-21</v>
@@ -9129,7 +9129,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9282,7 +9282,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9292,14 +9292,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9326,14 +9326,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9350,7 +9350,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9360,14 +9360,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9377,14 +9377,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9418,7 +9418,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9428,14 +9428,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9445,14 +9445,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9462,14 +9462,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9588,7 +9588,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9598,14 +9598,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9615,14 +9615,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9639,7 +9639,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9656,7 +9656,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9666,14 +9666,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9690,7 +9690,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9700,14 +9700,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9955,14 +9955,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9979,7 +9979,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9989,14 +9989,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10006,14 +10006,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10023,14 +10023,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10040,14 +10040,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10098,7 +10098,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10149,7 +10149,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10183,7 +10183,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10200,7 +10200,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10217,7 +10217,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10227,14 +10227,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10244,14 +10244,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10268,7 +10268,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10285,7 +10285,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10319,7 +10319,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10336,7 +10336,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10346,14 +10346,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10363,14 +10363,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10404,7 +10404,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10421,7 +10421,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10431,14 +10431,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10448,14 +10448,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10472,7 +10472,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10489,7 +10489,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10506,7 +10506,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10523,7 +10523,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10540,7 +10540,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10557,7 +10557,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10591,7 +10591,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10601,14 +10601,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10625,7 +10625,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10642,7 +10642,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10652,14 +10652,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10676,7 +10676,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10686,14 +10686,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10710,7 +10710,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10727,7 +10727,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10744,7 +10744,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10761,7 +10761,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10778,7 +10778,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10795,7 +10795,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10812,7 +10812,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,7 +10829,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10846,7 +10846,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10863,7 +10863,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10880,7 +10880,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10914,7 +10914,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10924,14 +10924,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10941,14 +10941,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10958,14 +10958,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11009,14 +11009,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11026,14 +11026,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11043,14 +11043,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11060,14 +11060,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11077,14 +11077,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11101,7 +11101,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11111,14 +11111,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11135,7 +11135,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11169,7 +11169,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11179,14 +11179,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11196,14 +11196,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11220,7 +11220,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11254,7 +11254,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11271,7 +11271,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11305,7 +11305,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11315,14 +11315,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11332,14 +11332,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11356,7 +11356,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11373,7 +11373,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11390,7 +11390,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11407,7 +11407,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11424,7 +11424,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11434,14 +11434,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11451,14 +11451,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11475,7 +11475,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11492,7 +11492,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11509,7 +11509,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11543,7 +11543,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11560,7 +11560,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11577,7 +11577,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11628,7 +11628,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11645,7 +11645,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11662,7 +11662,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11672,14 +11672,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11696,7 +11696,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11713,7 +11713,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11723,14 +11723,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11747,7 +11747,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11764,7 +11764,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11781,7 +11781,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11798,7 +11798,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11815,7 +11815,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11832,7 +11832,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11849,7 +11849,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11866,7 +11866,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11883,7 +11883,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11900,7 +11900,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11917,7 +11917,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11934,7 +11934,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11944,14 +11944,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11968,7 +11968,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11978,14 +11978,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12019,7 +12019,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12036,7 +12036,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12053,7 +12053,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12070,7 +12070,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12080,14 +12080,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12097,14 +12097,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12121,7 +12121,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12138,7 +12138,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12155,7 +12155,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12172,7 +12172,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12182,14 +12182,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12206,7 +12206,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12223,7 +12223,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12240,7 +12240,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12257,7 +12257,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12274,7 +12274,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12291,7 +12291,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12308,7 +12308,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12325,7 +12325,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12342,7 +12342,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12359,7 +12359,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12376,7 +12376,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12393,7 +12393,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12403,14 +12403,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12427,7 +12427,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12444,7 +12444,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12461,7 +12461,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12478,7 +12478,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12495,7 +12495,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12512,7 +12512,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12529,7 +12529,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12546,7 +12546,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12556,14 +12556,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12580,7 +12580,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12590,14 +12590,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12614,7 +12614,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12631,7 +12631,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12648,7 +12648,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12665,7 +12665,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12682,7 +12682,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12699,7 +12699,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12709,14 +12709,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12733,7 +12733,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12750,7 +12750,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12767,7 +12767,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12784,7 +12784,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12801,7 +12801,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12818,7 +12818,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12828,14 +12828,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12852,7 +12852,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12862,14 +12862,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12903,7 +12903,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12920,7 +12920,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12937,7 +12937,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12954,7 +12954,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12964,14 +12964,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12988,7 +12988,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13005,7 +13005,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13022,7 +13022,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13032,14 +13032,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13056,7 +13056,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13073,7 +13073,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13090,7 +13090,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13107,7 +13107,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13124,7 +13124,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13158,7 +13158,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13175,7 +13175,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13192,7 +13192,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13202,14 +13202,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13226,7 +13226,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13243,7 +13243,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13260,7 +13260,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13277,7 +13277,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13311,7 +13311,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13328,7 +13328,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13345,7 +13345,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13362,7 +13362,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13372,14 +13372,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13389,14 +13389,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13413,7 +13413,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13440,14 +13440,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13464,7 +13464,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13474,14 +13474,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13498,7 +13498,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13508,14 +13508,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13532,7 +13532,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13566,7 +13566,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13576,14 +13576,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13617,7 +13617,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13634,7 +13634,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13651,7 +13651,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13668,7 +13668,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13685,7 +13685,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13702,7 +13702,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13719,7 +13719,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13736,7 +13736,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13753,7 +13753,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13763,14 +13763,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13787,7 +13787,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13804,7 +13804,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13821,7 +13821,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13838,7 +13838,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13855,7 +13855,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13872,7 +13872,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13889,7 +13889,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13906,7 +13906,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13923,7 +13923,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13940,7 +13940,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13957,7 +13957,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13991,7 +13991,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14008,7 +14008,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14025,7 +14025,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14042,7 +14042,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14059,7 +14059,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14069,14 +14069,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14093,7 +14093,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14110,7 +14110,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14127,7 +14127,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14154,14 +14154,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14178,7 +14178,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14188,14 +14188,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14205,14 +14205,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14229,7 +14229,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14239,14 +14239,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14263,7 +14263,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14280,7 +14280,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14297,7 +14297,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14314,7 +14314,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14331,7 +14331,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14348,7 +14348,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14365,7 +14365,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14382,7 +14382,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14399,7 +14399,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14416,7 +14416,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14433,7 +14433,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14450,7 +14450,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14460,14 +14460,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14484,7 +14484,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14494,14 +14494,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14518,7 +14518,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14535,7 +14535,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14552,7 +14552,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14569,7 +14569,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14586,7 +14586,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14603,7 +14603,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14620,7 +14620,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14630,14 +14630,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14647,14 +14647,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14671,7 +14671,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14681,14 +14681,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14705,7 +14705,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14722,7 +14722,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14739,7 +14739,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14756,7 +14756,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14773,7 +14773,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14790,7 +14790,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14807,7 +14807,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14841,7 +14841,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14875,7 +14875,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14892,7 +14892,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14909,7 +14909,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14926,7 +14926,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14943,7 +14943,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14960,7 +14960,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14977,7 +14977,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14994,7 +14994,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15011,7 +15011,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15028,7 +15028,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15045,7 +15045,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15062,7 +15062,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15072,14 +15072,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15096,7 +15096,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15113,7 +15113,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15130,7 +15130,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15140,14 +15140,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15157,14 +15157,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15181,7 +15181,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15198,7 +15198,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15208,14 +15208,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15232,7 +15232,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15249,7 +15249,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15266,7 +15266,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15283,7 +15283,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15300,7 +15300,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15317,7 +15317,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15351,7 +15351,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15368,7 +15368,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15385,7 +15385,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15402,7 +15402,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15419,7 +15419,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15436,7 +15436,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15446,14 +15446,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15463,14 +15463,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15480,14 +15480,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15504,7 +15504,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15514,14 +15514,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15531,14 +15531,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15548,14 +15548,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15589,7 +15589,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15623,7 +15623,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15633,14 +15633,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15657,7 +15657,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15674,7 +15674,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15691,7 +15691,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15708,7 +15708,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15725,7 +15725,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15742,7 +15742,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15759,7 +15759,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15776,7 +15776,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15810,7 +15810,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15827,7 +15827,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15844,7 +15844,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15854,14 +15854,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15878,7 +15878,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -15929,7 +15929,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15946,7 +15946,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -15956,14 +15956,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -15973,14 +15973,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -15997,7 +15997,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16024,14 +16024,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16041,14 +16041,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16065,7 +16065,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16075,14 +16075,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16099,7 +16099,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16109,14 +16109,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16126,14 +16126,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16143,14 +16143,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16160,14 +16160,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16177,14 +16177,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16201,7 +16201,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16211,14 +16211,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16228,14 +16228,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16245,14 +16245,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16262,14 +16262,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16296,14 +16296,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16347,14 +16347,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16364,14 +16364,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16381,14 +16381,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16398,14 +16398,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16422,7 +16422,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16439,7 +16439,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16449,14 +16449,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16473,7 +16473,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16483,14 +16483,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16500,14 +16500,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16524,7 +16524,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16534,14 +16534,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16558,7 +16558,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16575,7 +16575,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16592,7 +16592,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16602,14 +16602,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16619,14 +16619,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16636,14 +16636,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16653,14 +16653,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16670,14 +16670,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16694,7 +16694,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16728,7 +16728,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16738,14 +16738,14 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -16772,14 +16772,14 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16796,7 +16796,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16813,7 +16813,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16830,7 +16830,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16847,7 +16847,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16864,7 +16864,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16881,7 +16881,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16891,14 +16891,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16908,14 +16908,14 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16925,14 +16925,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -16942,14 +16942,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16976,14 +16976,14 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17010,14 +17010,14 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17027,14 +17027,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17044,14 +17044,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17061,14 +17061,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17078,14 +17078,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17095,14 +17095,14 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17119,7 +17119,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17129,14 +17129,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17146,14 +17146,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17163,14 +17163,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17180,14 +17180,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17204,7 +17204,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17214,14 +17214,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17238,7 +17238,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17248,14 +17248,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17265,14 +17265,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17282,14 +17282,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17306,7 +17306,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17316,14 +17316,14 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17333,14 +17333,14 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17350,14 +17350,14 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17374,7 +17374,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17384,14 +17384,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17401,14 +17401,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17425,7 +17425,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17435,14 +17435,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17452,14 +17452,14 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17476,7 +17476,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17493,7 +17493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17527,7 +17527,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17537,14 +17537,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17554,14 +17554,14 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17571,14 +17571,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17588,14 +17588,14 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17605,14 +17605,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17622,14 +17622,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17639,14 +17639,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17656,14 +17656,14 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17673,14 +17673,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -17748,7 +17748,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17758,14 +17758,14 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17809,14 +17809,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17826,14 +17826,14 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17843,14 +17843,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -17867,7 +17867,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -17894,14 +17894,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -17918,7 +17918,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -17952,7 +17952,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -17969,7 +17969,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -17986,7 +17986,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -18003,7 +18003,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -18013,14 +18013,14 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18037,7 +18037,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18047,14 +18047,14 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18064,14 +18064,14 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18081,14 +18081,14 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18098,14 +18098,14 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18115,14 +18115,14 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18139,7 +18139,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18183,14 +18183,14 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18207,7 +18207,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18224,7 +18224,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18241,7 +18241,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18258,7 +18258,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18268,14 +18268,14 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18309,7 +18309,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18319,14 +18319,14 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18343,7 +18343,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18370,14 +18370,14 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18394,7 +18394,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18404,14 +18404,14 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18421,14 +18421,14 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18438,14 +18438,14 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18455,14 +18455,14 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18479,7 +18479,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18489,14 +18489,14 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -18506,14 +18506,14 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -18530,7 +18530,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -18547,7 +18547,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -18557,14 +18557,14 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -18581,7 +18581,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -18591,14 +18591,14 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18608,14 +18608,14 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18632,7 +18632,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18642,14 +18642,14 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18659,14 +18659,14 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18683,7 +18683,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18717,7 +18717,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18727,14 +18727,14 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18751,7 +18751,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18761,14 +18761,14 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18778,14 +18778,14 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18802,7 +18802,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18819,7 +18819,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -18829,14 +18829,14 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -18846,14 +18846,14 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -18870,7 +18870,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -18897,14 +18897,14 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -18921,7 +18921,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -18931,14 +18931,14 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -18948,14 +18948,14 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -18972,7 +18972,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -18989,7 +18989,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -18999,14 +18999,14 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -19016,14 +19016,14 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -19033,14 +19033,14 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -19050,14 +19050,14 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -19067,14 +19067,14 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -19091,7 +19091,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -19116,188 +19116,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004098510</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6.570000171661377</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3.805174938629898</v>
-      </c>
-      <c r="I2" t="n">
-        <v>105</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005245508</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3.157894736842105</v>
-      </c>
-      <c r="I3" t="n">
-        <v>49</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PLC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005339160</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2.680000066757202</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4.10447750970021</v>
-      </c>
-      <c r="I4" t="n">
-        <v>28</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19308,707 +19129,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Acinque S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B.F. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BESTBE HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CALEFFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DIGITAL BROS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Digital Value S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ESPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>EdgeLab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GEOX S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GEOX S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>HERA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>IMMSI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Neodecortech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RCS MediaGroup S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TENARIS S.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ZEST S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>